--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -1135,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L94"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1155,7 +1155,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>常规卡池 · 43 张（普 11 / 罕 19 / 稀 13 · §5.1–5.3）</t>
+          <t>常规卡池 · 80 张（普 20 / 罕 35 / 稀 25 · §5.1–5.3）</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -4921,7 +4921,7 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>v1.2 替换记录：三连骰→洗劫、出老千→叠注、催债人→连胜、铁赌桌→当铺、脚底抹油→高利贷、切牌→数牌、金库→买凶、威逼利诱→黑吃黑、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
+          <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
         </is>
       </c>
     </row>
@@ -4946,13 +4946,10 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B87:J87"/>
     <mergeCell ref="B90:J90"/>
-    <mergeCell ref="B87:J87"/>
     <mergeCell ref="B89:J89"/>
     <mergeCell ref="B88:J88"/>
     <mergeCell ref="B2:J2"/>
@@ -4969,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5102,7 +5099,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>私房钱</t>
+          <t>本钱</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -5166,10 +5163,11 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>两张签名牌让"产金"和"赌博"从第一回合就在场。私房钱 0 能白拿 5 金——产金基准（1 能量 = 7 金币）的免能量特例；试手气即赌博模板的教学样板。</t>
+          <t>两张签名牌让"产金"和"赌博"从第一回合就在场。本钱 0 能白拿 5 金——产金基准（1 能量 = 7 金币）的免能量特例；试手气即赌博模板的教学样板。</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -1135,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A2:L87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1155,7 +1155,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>常规卡池 · 80 张（普 20 / 罕 35 / 稀 25 · §5.1–5.3）</t>
+          <t>常规卡池 · 76 张（普 20 / 罕 33 / 稀 23 · §5.1–5.3）</t>
         </is>
       </c>
     </row>
@@ -2017,705 +2017,705 @@
       <c r="L21" s="11" t="n"/>
     </row>
     <row r="22" ht="38" customHeight="1">
-      <c r="B22" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="B22" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>连胜★</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>摇骰</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>赌博·连锁（上限2）</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>造成 5 伤害。赌博：正面 → 再次触发本效果并再次赌博（最多连锁 2 次）</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>基础 7 伤害</t>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>赌博·随机多段</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>5×3 / 正面每次 10</t>
         </is>
       </c>
       <c r="K22" s="11" t="n"/>
       <c r="L22" s="11" t="n"/>
     </row>
     <row r="23" ht="38" customHeight="1">
-      <c r="B23" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B23" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>摇骰</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>1能+5金</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>赌博·随机多段</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>5×3 / 正面每次 10</t>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>暗记</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>做局·下一掷必正</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>你的下一次赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>接下来 2 次必为正面</t>
         </is>
       </c>
       <c r="K23" s="11" t="n"/>
       <c r="L23" s="11" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="B24" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>暗记</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>派彩</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>做局·下一掷必正</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>你的下一次赌博必为正面</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>接下来 2 次必为正面</t>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>2能+3金</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>投资回本</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>获得 18 金币，抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>获得 22 金币</t>
         </is>
       </c>
       <c r="K24" s="11" t="n"/>
       <c r="L24" s="11" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="B25" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>派彩</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>数牌★</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>2能+3金</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>投资回本</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>获得 18 金币，抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>获得 22 金币</t>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>算牌·信息优势</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>顶 4 张</t>
         </is>
       </c>
       <c r="K25" s="11" t="n"/>
       <c r="L25" s="11" t="n"/>
     </row>
     <row r="26" ht="38" customHeight="1">
-      <c r="B26" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="B26" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>数牌★</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>兑筹★</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>算牌·信息优势</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>顶 4 张</t>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>牌换金·卡组精简</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>消耗手牌 1 张，获得 12 金币</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>获得 16 金币</t>
         </is>
       </c>
       <c r="K26" s="11" t="n"/>
       <c r="L26" s="11" t="n"/>
     </row>
     <row r="27" ht="38" customHeight="1">
-      <c r="B27" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B27" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>兑筹★</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>抽头</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>牌换金·卡组精简</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>消耗手牌 1 张，获得 12 金币</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>获得 16 金币</t>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>赌博·产金</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>获得 7 金币。赌博：正面 → 改为 14 金币</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>9 / 正面 18</t>
         </is>
       </c>
       <c r="K27" s="11" t="n"/>
       <c r="L27" s="11" t="n"/>
     </row>
     <row r="28" ht="38" customHeight="1">
-      <c r="B28" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="B28" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>抽头</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>保险</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>1能+2金</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>✔</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>赌博·产金</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>获得 7 金币。赌博：正面 → 改为 14 金币</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>9 / 正面 18</t>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>反向赌博（盼反面）</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>获得 8 格挡。赌博：反面 → 改为 16 格挡</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>10 / 反面 20</t>
         </is>
       </c>
       <c r="K28" s="11" t="n"/>
       <c r="L28" s="11" t="n"/>
     </row>
     <row r="29" ht="38" customHeight="1">
-      <c r="B29" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B29" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>保险</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>假筹</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>1能+2金</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>反向赌博（盼反面）</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>获得 8 格挡。赌博：反面 → 改为 16 格挡</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>10 / 反面 20</t>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>金币费用豁免</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>你的下一次金币花费不消耗金币</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>本场战斗前 2 次</t>
         </is>
       </c>
       <c r="K29" s="11" t="n"/>
       <c r="L29" s="11" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="B30" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>假筹</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>高利贷★</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>金币费用豁免</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>你的下一次金币花费不消耗金币</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>本场战斗前 2 次</t>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>跨战斗贷款</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>获得 18 金币</t>
         </is>
       </c>
       <c r="K30" s="11" t="n"/>
       <c r="L30" s="11" t="n"/>
     </row>
     <row r="31" ht="38" customHeight="1">
-      <c r="B31" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="B31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>高利贷★</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>跨战斗贷款</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>获得 18 金币</t>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>手气正旺</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>做局·被动概率</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>赌博正面率 +15%</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>+25%</t>
         </is>
       </c>
       <c r="K31" s="11" t="n"/>
       <c r="L31" s="11" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="B32" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>手气正旺</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>台规</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>做局·被动概率</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>赌博正面率 +15%</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>+25%</t>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>收入×正面联动</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>每回合开始获得 4 金币；每次掷出正面，额外获得 3 金币</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>每回合 5 金币</t>
         </is>
       </c>
       <c r="K32" s="11" t="n"/>
       <c r="L32" s="11" t="n"/>
     </row>
     <row r="33" ht="38" customHeight="1">
-      <c r="B33" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="B33" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>台规</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>流水</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>收入×正面联动</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>每回合开始获得 4 金币；每次掷出正面，额外获得 3 金币</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>每回合 5 金币</t>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>花费追踪·转抽牌</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>你每累计花费 10 金币，抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>每累计 8 金币</t>
         </is>
       </c>
       <c r="K33" s="11" t="n"/>
       <c r="L33" s="11" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>流水</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>花费追踪·转抽牌</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>你每累计花费 10 金币，抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
-        <is>
-          <t>每累计 8 金币</t>
+      <c r="B34" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>孤注一掷</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>1能+10金</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>真赌·尖刺</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>造成 27 伤害。赌博：正面 → 改为 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>正面 50 / 反面 29</t>
         </is>
       </c>
       <c r="K34" s="11" t="n"/>
       <c r="L34" s="11" t="n"/>
     </row>
     <row r="35" ht="54" customHeight="1">
-      <c r="B35" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="B35" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>孤注一掷</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>俄罗斯轮盘</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>1能+10金</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
         <is>
           <t>✔真赌</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>真赌·尖刺</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>造成 27 伤害。赌博：正面 → 改为 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>正面 50 / 反面 29</t>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>真赌·自伤多段</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>每次 4 / 正面 6</t>
         </is>
       </c>
       <c r="K35" s="11" t="n"/>
       <c r="L35" s="11" t="n"/>
     </row>
     <row r="36" ht="54" customHeight="1">
-      <c r="B36" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="B36" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>俄罗斯轮盘</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>爆机</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>✔真赌</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>真赌·自伤多段</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>每次 4 / 正面 6</t>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>3能+8金</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>头奖·击杀产金大</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>造成 35 伤害。击杀则获得 25 金币</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>40 伤害</t>
         </is>
       </c>
       <c r="K36" s="11" t="n"/>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="B37" s="9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>爆机</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -2742,27 +2742,27 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>3能+8金</t>
+          <t>3能+12金</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>头奖·击杀产金大</t>
+          <t>兑现·终结</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>造成 35 伤害。击杀则获得 25 金币</t>
+          <t>造成 43 伤害 ×倍率</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>40 伤害</t>
+          <t>46 伤害</t>
         </is>
       </c>
       <c r="K37" s="11" t="n"/>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="38" ht="38" customHeight="1">
       <c r="B38" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
@@ -2779,319 +2779,319 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>豹子</t>
+          <t>单双</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>✔×3</t>
+          <t>✔真赌</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>赌博·逐击独立</t>
+          <t>真赌·能量</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>造成 9 伤害 3 次，每击独立赌博：正面则该击改为 18</t>
+          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>每击 10 / 正面 20</t>
+          <t>正面 5 点能量</t>
         </is>
       </c>
       <c r="K38" s="11" t="n"/>
       <c r="L38" s="11" t="n"/>
     </row>
     <row r="39" ht="38" customHeight="1">
-      <c r="B39" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="B39" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>打庄★</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>3能+12金</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>兑现·终结</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>造成 43 伤害 ×倍率</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>46 伤害</t>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>2能+15金</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>定向斩杀（最低生命）</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>对生命值最低的敌人造成 43 伤害</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>50 伤害</t>
         </is>
       </c>
       <c r="K39" s="11" t="n"/>
       <c r="L39" s="11" t="n"/>
     </row>
     <row r="40" ht="38" customHeight="1">
-      <c r="B40" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="B40" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>单双</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>弃牌</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>✔真赌</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>真赌·能量</t>
-        </is>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
-        <is>
-          <t>正面 5 点能量</t>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>自消耗换值</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>抽 2 张牌，获得 14 金币</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>抽 3 张，18 金币</t>
         </is>
       </c>
       <c r="K40" s="11" t="n"/>
       <c r="L40" s="11" t="n"/>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="B41" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="B41" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>老虎机</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>抽佣★</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>2能+5金</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>✔×3</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>头奖·多次掷产金引擎</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>赌博 3 次，每次正面：获得 9 金币并抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>每次正面 11 金币</t>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>力量剥夺</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>施加 5 点力量削弱与 3 易伤</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>6 点力量削弱与 4 易伤</t>
         </is>
       </c>
       <c r="K41" s="11" t="n"/>
       <c r="L41" s="11" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="B42" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>打庄★</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>2能+15金</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>定向斩杀（最低生命）</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>对生命值最低的敌人造成 43 伤害</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>50 伤害</t>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>底牌</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>倍率条件·抽牌</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>抽 2 张牌。若倍率 ≥1.5，额外抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>抽 3 张牌</t>
         </is>
       </c>
       <c r="K42" s="11" t="n"/>
       <c r="L42" s="11" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="B43" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>弃牌</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>消耗</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>自消耗换值</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>抽 2 张牌，获得 14 金币</t>
-        </is>
-      </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>抽 3 张，18 金币</t>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>赌神</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>3能</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>做局·终极全正</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>你的所有赌博视为正面</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>费用变为 2</t>
         </is>
       </c>
       <c r="K43" s="11" t="n"/>
       <c r="L43" s="11" t="n"/>
     </row>
     <row r="44" ht="38" customHeight="1">
-      <c r="B44" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="B44" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>抽佣★</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>力量剥夺</t>
-        </is>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>施加 5 点力量削弱与 3 易伤</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>6 点力量削弱与 4 易伤</t>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>利滚利★</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>产金放大器</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>本场战斗中你每次获得金币时，额外获得 2 金币</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>额外 3 金币</t>
         </is>
       </c>
       <c r="K44" s="11" t="n"/>
@@ -3099,508 +3099,502 @@
     </row>
     <row r="45" ht="38" customHeight="1">
       <c r="B45" s="9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>收手</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>兑现·格挡</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>获得 5 格挡 ×倍率</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>8 格挡</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>乘胜</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>兑现·单体</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>造成 6 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>9 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="38" customHeight="1">
+      <c r="B47" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>割禾青</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>倍率折算·抽牌</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>每 0.5 倍率抽 1 张牌（至多 3 张）</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>至多 4 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>兑现</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>兑现·产金</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>获得 7 金币 ×倍率</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>获得 9 金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>通杀</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>2能+5金</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>兑现·AoE</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>对所有敌人造成 16 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>20 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="B50" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>底牌</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>晒冷</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>3能+15金</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>兑现·大炮</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>造成 50 伤害 ×倍率</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>62 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>追数</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>2能+8金</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>风头</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>兑现·击杀续风</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>造成 29 伤害 ×倍率；若击杀则本次不清空倍率</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>36 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="B52" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>割肉</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>倍率条件·抽牌</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>抽 2 张牌。若倍率 ≥1.5，额外抽 1 张牌</t>
-        </is>
-      </c>
-      <c r="J45" s="10" t="inlineStr">
-        <is>
-          <t>抽 3 张牌</t>
-        </is>
-      </c>
-      <c r="K45" s="11" t="n"/>
-      <c r="L45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="B46" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>赌神</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F46" s="13" t="inlineStr">
-        <is>
-          <t>3能</t>
-        </is>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>做局·终极全正</t>
-        </is>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>你的所有赌博视为正面</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>费用变为 2</t>
-        </is>
-      </c>
-      <c r="K46" s="11" t="n"/>
-      <c r="L46" s="11" t="n"/>
-    </row>
-    <row r="47" ht="38" customHeight="1">
-      <c r="B47" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>利滚利★</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>产金放大器</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币</t>
-        </is>
-      </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>额外 3 金币</t>
-        </is>
-      </c>
-      <c r="K47" s="11" t="n"/>
-      <c r="L47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>收手</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>风头</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>兑现·格挡</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>获得 5 格挡 ×倍率</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>8 格挡</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="B49" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>乘胜</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>兑现·单体</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>造成 6 伤害 ×倍率</t>
-        </is>
-      </c>
-      <c r="J49" s="10" t="inlineStr">
-        <is>
-          <t>9 伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>割禾青</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>倍率折算·抽牌</t>
-        </is>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>每 0.5 倍率抽 1 张牌（至多 3 张）</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
-        <is>
-          <t>至多 4 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>兑现</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F51" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>兑现·产金</t>
-        </is>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>获得 7 金币 ×倍率</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>获得 9 金币</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="B52" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>通杀</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="inlineStr">
-        <is>
-          <t>2能+5金</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>兑现·AoE</t>
-        </is>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>对所有敌人造成 16 伤害 ×倍率</t>
-        </is>
-      </c>
-      <c r="J52" s="13" t="inlineStr">
-        <is>
-          <t>20 伤害</t>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>兑现·自伤</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>获得 10 格挡 ×倍率；自身失去「倍率 ×3」生命</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>13 格挡</t>
         </is>
       </c>
     </row>
     <row r="53" ht="54" customHeight="1">
       <c r="B53" s="9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>散码</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>兑现·大炮</t>
+          <t>即时产金·弃牌堆</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>造成 50 伤害 ×倍率</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8）</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>62 伤害</t>
+          <t>至多 12</t>
         </is>
       </c>
     </row>
     <row r="54" ht="54" customHeight="1">
       <c r="B54" s="9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>买码</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>兑现·击杀续风</t>
+          <t>即时产金·敌人数</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>造成 29 伤害 ×倍率；若击杀则本次不清空倍率</t>
+          <t>每个敌人给予 5 金币</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>36 伤害</t>
+          <t>每敌人 7 金</t>
         </is>
       </c>
     </row>
     <row r="55" ht="54" customHeight="1">
       <c r="B55" s="9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>普通</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>吃水</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+4金</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>兑现·自伤</t>
+          <t>击杀产金·溢出转金</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>获得 10 格挡 ×倍率；自身失去「倍率 ×3」生命</t>
+          <t>造成 12 伤害；**溢出的伤害**转为金币</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>16 伤害</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="B56" s="9" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
@@ -3609,7 +3603,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>点码</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -3629,23 +3623,23 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>即时产金·弃牌堆</t>
+          <t>花费追踪·转格挡</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8）</t>
+          <t>获得 5 格挡；本回合每花费过 5 金币，额外 +3 格挡</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>每 5 金 +4</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="B57" s="9" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
@@ -3654,7 +3648,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>洗牌</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -3674,23 +3668,23 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>即时产金·敌人数</t>
+          <t>弃牌换抽</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>每个敌人给予 5 金币</t>
+          <t>弃置 1 张手牌，抽 2 张牌</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>每敌人 7 金</t>
+          <t>抽 3 张</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="B58" s="9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
@@ -3699,12 +3693,12 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>护池</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
@@ -3719,23 +3713,23 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>击杀产金·溢出转金</t>
+          <t>附加费·多段格挡</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>造成 12 伤害；**溢出的伤害**转为金币</t>
+          <t>获得 5 格挡 3 次</t>
         </is>
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>16 伤害</t>
+          <t>7 格挡 3 次</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="B59" s="9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
@@ -3744,7 +3738,7 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>换码</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -3754,168 +3748,168 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
+          <t>0能+6金</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>附加费·买能量</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>获得 2 点能量</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>获得 3 点</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>再加注</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>花费追踪·转格挡</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>获得 5 格挡；本回合每花费过 5 金币，额外 +3 格挡</t>
-        </is>
-      </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>每 5 金 +4</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>洗牌</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>可变投入·档位解锁</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>自动花费至多 9 金：造成 8 伤害；≥3 金另施加 2 易伤；≥6 金另抽 1 张；≥9 金再 +8 伤害</t>
+        </is>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>抽水</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>1能</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>弃牌换抽</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>弃置 1 张手牌，抽 2 张牌</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>抽 3 张</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="B61" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>护池</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>1能+4金</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>附加费·多段格挡</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>获得 5 格挡 3 次</t>
-        </is>
-      </c>
-      <c r="J61" s="10" t="inlineStr">
-        <is>
-          <t>7 格挡 3 次</t>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>即时产金·手牌数</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>每张手牌获得 1 金币（至多 8）</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>至多 12</t>
         </is>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="B62" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>换码</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>0能+6金</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>附加费·买能量</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>获得 2 点能量</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>获得 3 点</t>
+      <c r="B62" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>押宝</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>1能+5金</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>✔真赌</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>真赌·押 HP</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>造成 18 伤害。赌博：正面 → 25 伤害；反面 → 自己失去 6 点生命</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>24 / 31</t>
         </is>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="B63" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
@@ -3924,43 +3918,43 @@
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>再加注</t>
+          <t>反水</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>可变投入·档位解锁</t>
+          <t>赌博·格挡反击</t>
         </is>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>自动花费至多 9 金：造成 8 伤害；≥3 金另施加 2 易伤；≥6 金另抽 1 张；≥9 金再 +8 伤害</t>
+          <t>赌博：正面 → 获得 9 格挡并造成 9 伤害；反面 → 获得 5 格挡</t>
         </is>
       </c>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>12 伤害</t>
+          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="B64" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
@@ -3969,7 +3963,7 @@
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>叠码</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -3989,23 +3983,23 @@
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>即时产金·手牌数</t>
+          <t>做局·倍率注入</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8）</t>
+          <t>倍率 +1.0</t>
         </is>
       </c>
       <c r="J64" s="13" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>倍率 +1.5</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="B65" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
@@ -4014,43 +4008,43 @@
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>押宝</t>
+          <t>保底</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>真赌·押 HP</t>
+          <t>消耗堆协同·格挡</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>造成 18 伤害。赌博：正面 → 25 伤害；反面 → 自己失去 6 点生命</t>
+          <t>获得 10 格挡；每张**已消耗**的牌 +2 格挡（至多 +10）</t>
         </is>
       </c>
       <c r="J65" s="13" t="inlineStr">
         <is>
-          <t>24 / 31</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="B66" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
@@ -4059,7 +4053,7 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>反水</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -4069,33 +4063,33 @@
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>✔</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>赌博·格挡反击</t>
+          <t>花费追踪·转能量</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 9 格挡并造成 9 伤害；反面 → 获得 5 格挡</t>
+          <t>获得 1 点能量；本回合每花费过 10 金，额外 +1（至多 3）</t>
         </is>
       </c>
       <c r="J66" s="13" t="inlineStr">
         <is>
-          <t>11 / 6</t>
+          <t>每 8 金</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="B67" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
@@ -4104,7 +4098,7 @@
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>清码</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -4124,23 +4118,23 @@
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>做局·倍率注入</t>
+          <t>手牌换金</t>
         </is>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>倍率 +1.0</t>
+          <t>弃置全部手牌，每弃 1 张获得 4 金币</t>
         </is>
       </c>
       <c r="J67" s="13" t="inlineStr">
         <is>
-          <t>倍率 +1.5</t>
+          <t>每张 5 金</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="B68" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
@@ -4149,17 +4143,17 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>翻盘</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
@@ -4169,23 +4163,23 @@
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>消耗堆协同·格挡</t>
+          <t>生命条件</t>
         </is>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>获得 10 格挡；每张**已消耗**的牌 +2 格挡（至多 +10）</t>
+          <t>造成 10 伤害；若你的生命低于 50%，改为 24 伤害</t>
         </is>
       </c>
       <c r="J68" s="13" t="inlineStr">
         <is>
-          <t>12 格挡</t>
+          <t>14 / 30</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="B69" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
@@ -4194,17 +4188,17 @@
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>暗注</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
@@ -4214,23 +4208,23 @@
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>花费追踪·转能量</t>
+          <t>附加费·穿透</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>获得 1 点能量；本回合每花费过 10 金，额外 +1（至多 3）</t>
+          <t>造成 6 点**无视格挡**的伤害</t>
         </is>
       </c>
       <c r="J69" s="13" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>9 点</t>
         </is>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="B70" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
@@ -4239,7 +4233,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>抵押</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -4249,7 +4243,7 @@
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
@@ -4259,23 +4253,23 @@
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>手牌换金</t>
+          <t>特异·卖血换甲</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币</t>
+          <t>获得 12 格挡；自己失去 4 点生命</t>
         </is>
       </c>
       <c r="J70" s="13" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>16 格挡</t>
         </is>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="B71" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
@@ -4284,223 +4278,223 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>翻盘</t>
+          <t>换牌</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>特异·消耗换抽</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>消耗 1 张手牌，抽 2 张牌</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>抽 3 张</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>全下</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>1能+3金</t>
-        </is>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>生命条件</t>
-        </is>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>造成 10 伤害；若你的生命低于 50%，改为 24 伤害</t>
-        </is>
-      </c>
-      <c r="J71" s="13" t="inlineStr">
-        <is>
-          <t>14 / 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="B72" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>暗注</t>
-        </is>
-      </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="13" t="inlineStr">
-        <is>
-          <t>附加费·穿透</t>
-        </is>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>造成 6 点**无视格挡**的伤害</t>
-        </is>
-      </c>
-      <c r="J72" s="13" t="inlineStr">
-        <is>
-          <t>9 点</t>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>X能+7X金</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>附加费·X费多段</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>对随机敌人造成 9×X 伤害，共 X 次</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>金币费降为 5×X</t>
         </is>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="B73" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D73" s="13" t="inlineStr">
-        <is>
-          <t>连庄</t>
-        </is>
-      </c>
-      <c r="E73" s="13" t="inlineStr">
+      <c r="B73" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>出千</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
+      <c r="F73" s="10" t="inlineStr">
         <is>
           <t>2能</t>
         </is>
       </c>
-      <c r="G73" s="13" t="inlineStr">
-        <is>
-          <t>✔×3</t>
-        </is>
-      </c>
-      <c r="H73" s="13" t="inlineStr">
-        <is>
-          <t>赌博·累积多掷</t>
-        </is>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>掷硬币 3 次，每次正面获得 8 格挡</t>
-        </is>
-      </c>
-      <c r="J73" s="13" t="inlineStr">
-        <is>
-          <t>每次 10</t>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>做局·本回合全正</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>本回合你接下来的所有赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="B74" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="C74" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D74" s="13" t="inlineStr">
-        <is>
-          <t>抵押</t>
-        </is>
-      </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="B74" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>摊牌</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr">
-        <is>
-          <t>0能</t>
-        </is>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="13" t="inlineStr">
-        <is>
-          <t>特异·卖血换甲</t>
-        </is>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>获得 12 格挡；自己失去 4 点生命</t>
-        </is>
-      </c>
-      <c r="J74" s="13" t="inlineStr">
-        <is>
-          <t>16 格挡</t>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>特异·弃牌堆规模</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>对随机敌人造成「弃牌堆张数」伤害（至多 20）</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>至多 28</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
-      <c r="B75" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="C75" s="13" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D75" s="13" t="inlineStr">
-        <is>
-          <t>换牌</t>
-        </is>
-      </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="B75" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>保本</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="F75" s="13" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G75" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="13" t="inlineStr">
-        <is>
-          <t>特异·消耗换抽</t>
-        </is>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>消耗 1 张手牌，抽 2 张牌</t>
-        </is>
-      </c>
-      <c r="J75" s="13" t="inlineStr">
-        <is>
-          <t>抽 3 张</t>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>特异·金币转格挡</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>消耗你一半金币，获得等量格挡（至多 30）</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>至多 40</t>
         </is>
       </c>
     </row>
     <row r="76" ht="54" customHeight="1">
       <c r="B76" s="9" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
@@ -4509,7 +4503,7 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>全下</t>
+          <t>押牌</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
@@ -4519,33 +4513,33 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>X能+7X金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✔真赌</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>附加费·X费多段</t>
+          <t>真赌·押手牌</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>对随机敌人造成 9×X 伤害，共 X 次</t>
+          <t>造成 8 伤害。赌博：正面 → 15 伤害；反面 → 弃掉 2 张手牌</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>金币费降为 5×X</t>
+          <t>12 / 19</t>
         </is>
       </c>
     </row>
     <row r="77" ht="54" customHeight="1">
       <c r="B77" s="9" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
@@ -4554,17 +4548,17 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>出千</t>
+          <t>截胡</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>2能+8金</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -4574,23 +4568,23 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>做局·本回合全正</t>
+          <t>击杀产金·处决</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>本回合你接下来的所有赌博必为正面</t>
+          <t>对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>26 伤害</t>
         </is>
       </c>
     </row>
     <row r="78" ht="54" customHeight="1">
       <c r="B78" s="9" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
@@ -4599,7 +4593,7 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>摊牌</t>
+          <t>倍投</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
@@ -4619,23 +4613,23 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>特异·弃牌堆规模</t>
+          <t>做局·倍率翻倍</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>对随机敌人造成「弃牌堆张数」伤害（至多 20）</t>
+          <t>你的倍率**翻倍**</t>
         </is>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>费用变为 1</t>
         </is>
       </c>
     </row>
     <row r="79" ht="54" customHeight="1">
       <c r="B79" s="9" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
@@ -4644,7 +4638,7 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>保本</t>
+          <t>换筹</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
@@ -4654,33 +4648,33 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>风头</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>特异·金币转格挡</t>
+          <t>风头·兑现能量</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>消耗你一半金币，获得等量格挡（至多 30）</t>
+          <t>按倍率折算能量：获得「倍率取整」点能量，结算后清空</t>
         </is>
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>至多 40</t>
+          <t>+1 点</t>
         </is>
       </c>
     </row>
     <row r="80" ht="54" customHeight="1">
       <c r="B80" s="9" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
@@ -4689,7 +4683,7 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>满贯</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
@@ -4699,248 +4693,68 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>2能+18金</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>真赌·押手牌</t>
+          <t>特异·赌博计数</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>造成 8 伤害。赌博：正面 → 15 伤害；反面 → 弃掉 2 张手牌</t>
+          <t>造成 30 伤害；若本场战斗中你掷出过正面，改为 50 伤害</t>
         </is>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>12 / 19</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="54" customHeight="1">
-      <c r="B81" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>截胡</t>
-        </is>
-      </c>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>2能+8金</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>击杀产金·处决</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币</t>
-        </is>
-      </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>26 伤害</t>
-        </is>
-      </c>
-    </row>
+          <t>38 / 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="54" customHeight="1"/>
     <row r="82" ht="54" customHeight="1">
-      <c r="B82" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="inlineStr">
-        <is>
-          <t>倍投</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>做局·倍率翻倍</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>你的倍率**翻倍**</t>
-        </is>
-      </c>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>费用变为 1</t>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条（"风头"= 带「风头正盛」词条，v1.6 新增），真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均已按当前代码实装校对。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="54" customHeight="1">
-      <c r="B83" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>换筹</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr">
-        <is>
-          <t>风头</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>风头·兑现能量</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>按倍率折算能量：获得「倍率取整」点能量，结算后清空</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>+1 点</t>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>v1.2 重设计原则：一张卡 = 一个钩子。消灭纯数值变体，每张卡在"钩子"列声明其独有机制，同家族不重复占位。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="54" customHeight="1">
-      <c r="B84" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>满贯</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>2能+18金</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>特异·赌博计数</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>造成 30 伤害；若本场战斗中你掷出过正面，改为 50 伤害</t>
-        </is>
-      </c>
-      <c r="J84" s="10" t="inlineStr">
-        <is>
-          <t>38 / 62</t>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>v1.3 评审删除：「换骰」「操纵牌局」——不做重掷机制，删后不补新卡（卡池 45→43，编号已重排，见设计文档 §5）。</t>
+        </is>
+      </c>
+    </row>
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条（"风头"= 带「风头正盛」词条，v1.6 新增），真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均已按当前代码实装校对。</t>
+          <t>实装同步注记（以代码为准）：加注为自动花费至多 6 金币（选额 UI 留美术资产批）；数牌为选 1 张置入弃牌堆；底牌正面改为额外抽 1 张（原设计"费用 -1"待费用修改器接入后还原）。</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
-        <is>
-          <t>v1.2 重设计原则：一张卡 = 一个钩子。消灭纯数值变体，每张卡在"钩子"列声明其独有机制，同家族不重复占位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>v1.3 评审删除：「换骰」「操纵牌局」——不做重掷机制，删后不补新卡（卡池 45→43，编号已重排，见设计文档 §5）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>实装同步注记（以代码为准）：加注为自动花费至多 6 金币（选额 UI 留美术资产批）；数牌为选 1 张置入弃牌堆；底牌正面改为额外抽 1 张（原设计"费用 -1"待费用修改器接入后还原）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
         <is>
           <t>注：「保险」是反向赌博（反面才强化），全池唯一一张"盼反面"的普通赌博牌，为真赌牌和做局留心理准备。</t>
         </is>
@@ -4966,7 +4780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5163,7 +4977,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -1135,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L87"/>
+  <dimension ref="A2:L100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1155,7 +1155,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>常规卡池 · 76 张（普 20 / 罕 33 / 稀 23 · §5.1–5.3）</t>
+          <t>常规卡池 · 85 张（普 24 / 罕 35 / 稀 26 · §5.1–5.3）</t>
         </is>
       </c>
     </row>
@@ -4717,49 +4717,458 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="54" customHeight="1"/>
+    <row r="81" ht="54" customHeight="1">
+      <c r="B81" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>封口</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>出千·必正生成</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>获得 1 次必正，抽 1 张牌</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>获得 2 次必正</t>
+        </is>
+      </c>
+    </row>
     <row r="82" ht="54" customHeight="1">
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>偷天换日</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>出千·赌博转必正</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>造成 5 伤害。赌博：正面 → 额外获得 1 次必正</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>造成 8 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="54" customHeight="1">
+      <c r="B83" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>血本</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>0能</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>赌命·自伤换能量</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>失去 5 点生命，获得 2 点能量</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>失去 4 点生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="54" customHeight="1">
+      <c r="B84" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>放血</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>赌命·自伤输出</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>造成 9 伤害，自己失去 3 点生命</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>造成 12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>收网</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>出千·必正兑现</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>消耗所有必正，每 1 次造成 9 伤害</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>每次 12 伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>押注</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>赌命·伤害加成</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>你造成的伤害 +「已失去生命」的 10%</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>千王</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>出千·正面转必正</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>1能+6金</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>出千·本回合全正</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>本回合你接下来的 3 次赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>赌命</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>赌命·血线大炮</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>造成「你已失去生命」50% 的伤害</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="B91" t="inlineStr">
         <is>
           <t>费用列简写："1能+5金" = 1 能量 + 5 金币；赌博列"✔"表示带赌博词条（"风头"= 带「风头正盛」词条，v1.6 新增），真赌标注反面惩罚；★ = v1.2 新钩子卡；效果列均已按当前代码实装校对。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="54" customHeight="1">
-      <c r="B83" t="inlineStr">
+    <row r="92">
+      <c r="B92" t="inlineStr">
         <is>
           <t>v1.2 重设计原则：一张卡 = 一个钩子。消灭纯数值变体，每张卡在"钩子"列声明其独有机制，同家族不重复占位。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="54" customHeight="1">
-      <c r="B84" t="inlineStr">
+    <row r="93">
+      <c r="B93" t="inlineStr">
         <is>
           <t>v1.2 替换记录（旧名→当前名）：三连骰→清台、出老千→叠注、催债人→连胜、铁赌桌→兑筹、脚底抹油→高利贷、切牌→数牌、金库→打庄、威逼利诱→抽佣、摇钱树→利滚利；加注由固定附加费改为可变投入。</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
+    <row r="94">
+      <c r="B94" t="inlineStr">
         <is>
           <t>v1.3 评审删除：「换骰」「操纵牌局」——不做重掷机制，删后不补新卡（卡池 45→43，编号已重排，见设计文档 §5）。</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
+    <row r="95">
+      <c r="B95" t="inlineStr">
         <is>
           <t>实装同步注记（以代码为准）：加注为自动花费至多 6 金币（选额 UI 留美术资产批）；数牌为选 1 张置入弃牌堆；底牌正面改为额外抽 1 张（原设计"费用 -1"待费用修改器接入后还原）。</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
+    <row r="96">
+      <c r="B96" t="inlineStr">
         <is>
           <t>注：「保险」是反向赌博（反面才强化），全池唯一一张"盼反面"的普通赌博牌，为真赌牌和做局留心理准备。</t>
         </is>
       </c>
     </row>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B87:J87"/>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -406,7 +406,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -536,6 +536,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -684,7 +728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -723,6 +767,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1135,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L100"/>
+  <dimension ref="B2:L96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1253,12 +1299,12 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>造成 10 伤害</t>
+          <t>造成 11 伤害</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>造成 13 伤害</t>
+          <t>造成 14 伤害</t>
         </is>
       </c>
       <c r="K5" s="11" t="n"/>
@@ -1275,7 +1321,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>加注★</t>
+          <t>加注</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -1295,17 +1341,17 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>可变投入·小额</t>
+          <t>花费追踪·每金 +1 伤</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>造成 6 伤害。可额外花费至多 6 金币，每 1 金币 +2 伤害</t>
+          <t>造成 7 伤害。本回合每花费 1 金币，伤害 +1</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>基础 8 伤害</t>
+          <t>基础 10 伤害</t>
         </is>
       </c>
       <c r="K6" s="11" t="n"/>
@@ -1332,7 +1378,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1379,7 +1425,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -1394,12 +1440,12 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>造成 16 伤害，施加 1 易伤</t>
+          <t>造成 14 伤害，施加 2 易伤</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>19 伤害，2 易伤</t>
+          <t>17 伤害，2 易伤</t>
         </is>
       </c>
       <c r="K8" s="11" t="n"/>
@@ -1441,12 +1487,12 @@
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>造成 7 伤害。击杀则获得 10 金币</t>
+          <t>造成 9 伤害。击杀则获得 15 金币</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>9 伤害，击杀 +14 金</t>
+          <t>11 伤害，击杀 +19 金</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -1520,7 +1566,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -1582,12 +1628,12 @@
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>获得 4 格挡。赌博：正面 → 改为 8 格挡</t>
+          <t>获得 5 格挡。赌博：正面 → 改为 9 格挡</t>
         </is>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>6 / 正面 13</t>
+          <t>7 / 正面 13</t>
         </is>
       </c>
       <c r="K12" s="11" t="n"/>
@@ -1614,7 +1660,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>0能+4金</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -1629,12 +1675,12 @@
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
+          <t>抽 2 张牌</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
           <t>抽 3 张牌</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>抽 4 张牌</t>
         </is>
       </c>
       <c r="K13" s="11" t="n"/>
@@ -1661,7 +1707,7 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -1676,12 +1722,12 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
+          <t>施加 3 虚弱</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
           <t>施加 4 虚弱</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>施加 5 虚弱</t>
         </is>
       </c>
       <c r="K14" s="11" t="n"/>
@@ -1839,7 +1885,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>清台★</t>
+          <t>清台</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1933,7 +1979,7 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>叠注★</t>
+          <t>叠注</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -2099,12 +2145,12 @@
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>你的下一次赌博必为正面</t>
+          <t>你接下来的 2 次赌博必为正面</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>接下来 2 次必为正面</t>
+          <t>接下来 3 次必为正面</t>
         </is>
       </c>
       <c r="K23" s="11" t="n"/>
@@ -2168,7 +2214,7 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>数牌★</t>
+          <t>数牌</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -2215,7 +2261,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>兑筹★</t>
+          <t>兑筹</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -2403,7 +2449,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>高利贷★</t>
+          <t>高利贷</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -2826,7 +2872,7 @@
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>打庄★</t>
+          <t>打庄</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -2920,7 +2966,7 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>抽佣★</t>
+          <t>抽佣</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -3061,7 +3107,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>利滚利★</t>
+          <t>利滚利</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -3133,12 +3179,12 @@
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>获得 5 格挡 ×倍率</t>
+          <t>获得 6 格挡 ×倍率</t>
         </is>
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>8 格挡</t>
+          <t>9 格挡</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3224,12 @@
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
-          <t>造成 6 伤害 ×倍率</t>
+          <t>造成 7 伤害 ×倍率</t>
         </is>
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>9 伤害</t>
+          <t>10 伤害</t>
         </is>
       </c>
     </row>
@@ -3493,12 +3539,12 @@
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>每 2 张弃牌堆的牌，获得 1 金币（至多 8）</t>
+          <t>每 2 张弃牌堆的牌，获得 1 金币（不设上限）</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>额外抽 1 张</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3614,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -3578,17 +3624,17 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>击杀产金·溢出转金</t>
+          <t>即时产金·破盾转金</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
-          <t>造成 12 伤害；**溢出的伤害**转为金币</t>
+          <t>造成 16 伤害；被格挡抵消的伤害转为金币</t>
         </is>
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>16 伤害</t>
+          <t>20 伤害</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3674,12 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>获得 5 格挡；本回合每花费过 5 金币，额外 +3 格挡</t>
+          <t>获得 5 格挡；本回合每花费 1 金币，额外 +1 格挡</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>每 5 金 +4</t>
+          <t>基础 8 格挡</t>
         </is>
       </c>
     </row>
@@ -3668,17 +3714,17 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>弃牌换抽</t>
+          <t>牌换金·小额</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>弃置 1 张手牌，抽 2 张牌</t>
+          <t>消耗 1 张手牌，获得 6 金币</t>
         </is>
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>获得 8 金币</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3749,7 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>0能+5金</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
@@ -3718,12 +3764,12 @@
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>获得 5 格挡 3 次</t>
+          <t>获得 4 格挡 4 次</t>
         </is>
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>7 格挡 3 次</t>
+          <t>6 格挡 4 次</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3794,7 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>0能+6金</t>
+          <t>0能+2金</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -3763,12 +3809,12 @@
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>获得 2 点能量</t>
+          <t>获得 1 点能量</t>
         </is>
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>获得 3 点</t>
+          <t>获得 2 点</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4389,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>附加费·X费多段</t>
+          <t>可变投入·X费多段</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -4753,12 +4799,12 @@
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>获得 1 次必正，抽 1 张牌</t>
+          <t>抽 2 张牌</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>获得 2 次必正</t>
+          <t>获得 2 次必正，抽 2 张牌</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4864,12 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>血本</t>
+          <t>分红</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
@@ -4838,17 +4884,17 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>赌命·自伤换能量</t>
+          <t>收入引擎·买血</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>失去 5 点生命，获得 2 点能量</t>
+          <t>每回合开始支付 3 金币，回复 1 点生命（金币不足 3 时不触发）</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>失去 4 点生命</t>
+          <t>回复 2 点生命</t>
         </is>
       </c>
     </row>
@@ -4868,12 +4914,12 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
@@ -4883,17 +4929,17 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>赌命·自伤输出</t>
+          <t>赌命·自伤产金</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>造成 9 伤害，自己失去 3 点生命</t>
+          <t>失去 2 点生命，获得 20 金币</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>造成 12 伤害</t>
+          <t>获得 26 金币</t>
         </is>
       </c>
     </row>
@@ -4946,181 +4992,53 @@
       <c r="B86" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>押注</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F86" s="10" t="inlineStr">
-        <is>
-          <t>1能</t>
-        </is>
-      </c>
-      <c r="G86" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>赌命·伤害加成</t>
-        </is>
-      </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>你造成的伤害 +「已失去生命」的 10%</t>
-        </is>
-      </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
+      <c r="C86" s="14" t="n"/>
+      <c r="D86" s="14" t="n"/>
+      <c r="E86" s="14" t="n"/>
+      <c r="F86" s="14" t="n"/>
+      <c r="G86" s="14" t="n"/>
+      <c r="H86" s="14" t="n"/>
+      <c r="I86" s="14" t="n"/>
+      <c r="J86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="B87" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>千王</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t>2能</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>出千·正面转必正</t>
-        </is>
-      </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>每回合前 1 次掷出正面时，获得 1 次必正</t>
-        </is>
-      </c>
-      <c r="J87" s="10" t="inlineStr">
-        <is>
-          <t>前 2 次</t>
-        </is>
-      </c>
+      <c r="C87" s="14" t="n"/>
+      <c r="D87" s="14" t="n"/>
+      <c r="E87" s="14" t="n"/>
+      <c r="F87" s="14" t="n"/>
+      <c r="G87" s="14" t="n"/>
+      <c r="H87" s="14" t="n"/>
+      <c r="I87" s="14" t="n"/>
+      <c r="J87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="B88" s="9" t="n">
         <v>88</v>
       </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr">
-        <is>
-          <t>瞒天过海</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t>1能+6金</t>
-        </is>
-      </c>
-      <c r="G88" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>出千·本回合全正</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>本回合你接下来的 3 次赌博必为正面</t>
-        </is>
-      </c>
-      <c r="J88" s="10" t="inlineStr">
-        <is>
-          <t>4 次</t>
-        </is>
-      </c>
+      <c r="C88" s="14" t="n"/>
+      <c r="D88" s="14" t="n"/>
+      <c r="E88" s="14" t="n"/>
+      <c r="F88" s="14" t="n"/>
+      <c r="G88" s="14" t="n"/>
+      <c r="H88" s="14" t="n"/>
+      <c r="I88" s="14" t="n"/>
+      <c r="J88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="B89" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>赌命</t>
-        </is>
-      </c>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>2能+10金</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>赌命·血线大炮</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>造成「你已失去生命」50% 的伤害</t>
-        </is>
-      </c>
-      <c r="J89" s="10" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="14" t="n"/>
+      <c r="E89" s="14" t="n"/>
+      <c r="F89" s="14" t="n"/>
+      <c r="G89" s="14" t="n"/>
+      <c r="H89" s="14" t="n"/>
+      <c r="I89" s="14" t="n"/>
+      <c r="J89" s="15" t="n"/>
     </row>
     <row r="90"/>
     <row r="91">
@@ -5165,10 +5083,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B87:J87"/>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>X能+10X金</t>
+          <t>X能+5X金</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>造成 27×X 伤害</t>
+          <t>造成 20×X 伤害</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>金币费降为 8×X</t>
+          <t>金币费降为 4×X</t>
         </is>
       </c>
       <c r="K16" s="11" t="n"/>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>花费追踪·转伤害</t>
+          <t>花费追踪·追加伤害</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>造成 7 伤害。本回合每花费过 5 金币，额外 +4 伤害</t>
+          <t>造成 9 伤害。本回合若花费过金币，额外造成 1 次伤害</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>额外 +6 伤害</t>
+          <t>额外 2 次</t>
         </is>
       </c>
       <c r="K17" s="11" t="n"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>1能+4金</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>击杀产金·AoE收割</t>
+          <t>击杀产金·自我成长</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>对所有敌人造成 13 伤害。每击杀一个敌人，获得 7 金币</t>
+          <t>**消耗**。对所有敌人造成 13 伤害；每击杀一个敌人获得 7 金币；每打出一次，伤害永久 +4</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>造成 8 伤害。若倍率 ≥1.5，改为 16 伤害</t>
+          <t>造成 10 伤害。若倍率 ≥1.5，改为 20 伤害</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>10 / 20</t>
+          <t>12 / 24</t>
         </is>
       </c>
       <c r="K20" s="11" t="n"/>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>0能+10金</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>赌博·高方差尖刺</t>
+          <t>赌博·高方差产金</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>造成 10 伤害。赌博：正面 → 改为 20 伤害</t>
+          <t>硬币为正时：获得 25 金币；硬币为负时：获得 5 金币</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>13 / 正面 25</t>
+          <t>6 / 正面 30</t>
         </is>
       </c>
       <c r="K21" s="11" t="n"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>1能+5金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>对随机敌人造成 4 伤害 3 次。赌博：正面 → 每次 9</t>
+          <t>对随机敌人造成 4 伤害 4 次。赌博：正面 → 改为 6 次</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>5×3 / 正面每次 10</t>
+          <t>5×4 / 正面 5×6</t>
         </is>
       </c>
       <c r="K22" s="11" t="n"/>
@@ -3834,12 +3834,12 @@
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>0能+3金</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>可变投入·档位解锁</t>
+          <t>附加费·买活力</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>自动花费至多 9 金：造成 8 伤害；≥3 金另施加 2 易伤；≥6 金另抽 1 张；≥9 金再 +8 伤害</t>
+          <t>获得 5 点活力（下次攻击额外造成等量伤害）</t>
         </is>
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>12 伤害</t>
+          <t>8 点</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -2130,7 +2130,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+2金</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>2能+3金</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>获得 18 金币，抽 1 张牌</t>
+          <t>获得 18 金币，抽 2 张牌</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>算牌·信息优势</t>
+          <t>即时产金·手牌数</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>查看抽牌堆顶 3 张，可将其中任意张置入弃牌堆</t>
+          <t>每张手牌获得 2 金币</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>顶 4 张</t>
+          <t>每张 3 金币</t>
         </is>
       </c>
       <c r="K25" s="11" t="n"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>牌换金·卡组精简</t>
+          <t>附加费·买力量</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>消耗手牌 1 张，获得 12 金币</t>
+          <t>获得 2 点力量</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>获得 16 金币</t>
+          <t>获得 3 点力量</t>
         </is>
       </c>
       <c r="K26" s="11" t="n"/>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>获得 7 金币。赌博：正面 → 改为 14 金币</t>
+          <t>获得 10 金币。赌博：正面 → 改为 20 金币</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>9 / 正面 18</t>
+          <t>12 / 正面 24</t>
         </is>
       </c>
       <c r="K27" s="11" t="n"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>反向赌博（盼反面）</t>
+          <t>赌博·格挡</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>获得 8 格挡。赌博：反面 → 改为 16 格挡</t>
+          <t>获得 10 格挡。赌博：正面 → 改为 16 格挡</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>10 / 反面 20</t>
+          <t>12 / 正面 19</t>
         </is>
       </c>
       <c r="K28" s="11" t="n"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -2469,17 +2469,17 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>跨战斗贷款</t>
+          <t>借贷·回合利息</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>获得 14 金币。下场战斗开始时失去 6 金币（不足则全失）</t>
+          <t>获得 50 金币；此后每回合开始失去 5 金币</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>获得 18 金币</t>
+          <t>获得 60 金币</t>
         </is>
       </c>
       <c r="K30" s="11" t="n"/>
@@ -3894,17 +3894,17 @@
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>即时产金·手牌数</t>
+          <t>出千·必正与活力</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>每张手牌获得 1 金币（至多 8）</t>
+          <t>获得 2 次必正，以及 5 点活力</t>
         </is>
       </c>
       <c r="J61" s="13" t="inlineStr">
         <is>
-          <t>至多 12</t>
+          <t>3 次必正</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>造成 18 伤害。赌博：正面 → 25 伤害；反面 → 自己失去 6 点生命</t>
+          <t>造成 18 伤害。赌博：正面 → 30 伤害；反面 → 自己失去 3 点生命</t>
         </is>
       </c>
       <c r="J62" s="13" t="inlineStr">
         <is>
-          <t>24 / 31</t>
+          <t>24 / 正面 36 / 反面失 4</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>1能+3金</t>
+          <t>0能</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>造成 10 伤害；若你的生命低于 50%，改为 24 伤害</t>
+          <t>造成 6 伤害；若你的生命低于 50%，改为 14 伤害</t>
         </is>
       </c>
       <c r="J68" s="13" t="inlineStr">
         <is>
-          <t>14 / 30</t>
+          <t>8 / 18</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>造成 6 点**无视格挡**的伤害</t>
+          <t>造成 13 点**无视格挡**的伤害</t>
         </is>
       </c>
       <c r="J69" s="13" t="inlineStr">
         <is>
-          <t>9 点</t>
+          <t>16 点</t>
         </is>
       </c>
     </row>
@@ -4974,12 +4974,12 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>出千·必正兑现</t>
+          <t>出千·必正联动</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>消耗所有必正，每 1 次造成 9 伤害</t>
+          <t>你的每 1 次必正造成 9 伤害（不消耗必正）</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -2615,12 +2615,12 @@
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>你每累计花费 10 金币，抽 1 张牌</t>
+          <t>你每累计花费 6 金币，抽 1 张牌</t>
         </is>
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>每累计 8 金币</t>
+          <t>每累计 5 金币</t>
         </is>
       </c>
       <c r="K33" s="11" t="n"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>1能+2金</t>
+          <t>1能+3金</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 9 格挡并造成 9 伤害；反面 → 获得 5 格挡</t>
+          <t>硬币为正时：10 格挡 + 10 伤害；硬币为负时：6 格挡 + 6 伤害</t>
         </is>
       </c>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>正面 11 挡 + 11 伤 / 反面 6 挡</t>
+          <t>12+12 / 7+7</t>
         </is>
       </c>
     </row>
@@ -4074,17 +4074,17 @@
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>消耗堆协同·格挡</t>
+          <t>消耗堆协同·产金</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>获得 10 格挡；每张**已消耗**的牌 +2 格挡（至多 +10）</t>
+          <t>每张**已消耗**的牌，获得 2 金币</t>
         </is>
       </c>
       <c r="J65" s="13" t="inlineStr">
         <is>
-          <t>12 格挡</t>
+          <t>每张 3 金</t>
         </is>
       </c>
     </row>
@@ -4119,17 +4119,17 @@
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>花费追踪·转能量</t>
+          <t>持有量·转能量</t>
         </is>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>获得 1 点能量；本回合每花费过 10 金，额外 +1（至多 3）</t>
+          <t>获得 1 点能量；每拥有 50 金币，额外 +1（不设上限）</t>
         </is>
       </c>
       <c r="J66" s="13" t="inlineStr">
         <is>
-          <t>每 8 金</t>
+          <t>基础 2 能量</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>弃置全部手牌，每弃 1 张获得 4 金币</t>
+          <t>消耗全部手牌，每张获得 7 金币</t>
         </is>
       </c>
       <c r="J67" s="13" t="inlineStr">
         <is>
-          <t>每张 5 金</t>
+          <t>每张 9 金</t>
         </is>
       </c>
     </row>
@@ -4299,17 +4299,17 @@
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>特异·卖血换甲</t>
+          <t>特异·回牌换甲</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>获得 12 格挡；自己失去 4 点生命</t>
+          <t>将 1 张手牌放回抽牌堆，获得 9 格挡</t>
         </is>
       </c>
       <c r="J70" s="13" t="inlineStr">
         <is>
-          <t>16 格挡</t>
+          <t>12 格挡</t>
         </is>
       </c>
     </row>
@@ -4344,17 +4344,17 @@
       </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t>特异·消耗换抽</t>
+          <t>特异·重抽</t>
         </is>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
-          <t>消耗 1 张手牌，抽 2 张牌</t>
+          <t>将任意张手牌放回抽牌堆，再抽等量的牌</t>
         </is>
       </c>
       <c r="J71" s="13" t="inlineStr">
         <is>
-          <t>抽 3 张</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -2662,12 +2662,12 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>造成 27 伤害。赌博：正面 → 改为 43 伤害；反面 → 改为 25 伤害且自己受到 6 伤害</t>
+          <t>造成 30 伤害。赌博：正面 → 48 伤害；反面 → 28 伤害且自己受到 6 伤害</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>正面 50 / 反面 29</t>
+          <t>正面 55 / 反面 32</t>
         </is>
       </c>
       <c r="K34" s="11" t="n"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -2699,22 +2699,22 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>真赌·自伤多段</t>
+          <t>特异·随机轮盘</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>对随机敌人造成 3 伤害 5 次。赌博：正面 → 每次改为 5；反面 → 其中 2 发改为打自己（自己共受 10 伤害）</t>
+          <t>每回合开始随机开一枪：自己受到 3 伤害并获得 5 金币，或对随机敌人造成 10 伤害</t>
         </is>
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>每次 4 / 正面 6</t>
+          <t>自己 2 伤+7 金 / 敌人 14 伤</t>
         </is>
       </c>
       <c r="K35" s="11" t="n"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>3能+8金</t>
+          <t>3能+10金</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>造成 35 伤害。击杀则获得 25 金币</t>
+          <t>造成 40 伤害。击杀则获得 30 金币</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>40 伤害</t>
+          <t>46 伤害</t>
         </is>
       </c>
       <c r="K36" s="11" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>3能+12金</t>
+          <t>3能+10金</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>造成 43 伤害 ×倍率</t>
+          <t>造成 48 伤害 ×倍率</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>46 伤害</t>
+          <t>54 伤害</t>
         </is>
       </c>
       <c r="K37" s="11" t="n"/>
@@ -2840,22 +2840,22 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>✔真赌</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
-          <t>真赌·能量</t>
+          <t>特异·倍率奇偶</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>赌博：正面 → 获得 4 点能量；反面 → 失去 1 点能量</t>
+          <t>若倍率为偶数：获得 20 金币；若为奇数：获得 2 点力量与 2 点敏捷</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>正面 5 点能量</t>
+          <t>26 金 / 3+3</t>
         </is>
       </c>
       <c r="K38" s="11" t="n"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>2能+15金</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
@@ -2897,12 +2897,12 @@
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>对生命值最低的敌人造成 43 伤害</t>
+          <t>对生命值最低的敌人造成 15 伤害；若你的金币少于 100，伤害翻倍</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>50 伤害</t>
+          <t>19 / 翻倍 38</t>
         </is>
       </c>
       <c r="K39" s="11" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>抽 2 张牌，获得 14 金币</t>
+          <t>抽 2 张牌，获得 16 金币</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>抽 3 张，18 金币</t>
+          <t>抽 3 张，20 金币</t>
         </is>
       </c>
       <c r="K40" s="11" t="n"/>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+4金</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>施加 5 点力量削弱与 3 易伤</t>
+          <t>施加 6 点力量削弱与 4 易伤</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>6 点力量削弱与 4 易伤</t>
+          <t>8 点力量削弱与 5 易伤</t>
         </is>
       </c>
       <c r="K41" s="11" t="n"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>抽 2 张牌。若倍率 ≥1.5，额外抽 1 张牌</t>
+          <t>抽 3 张牌。若倍率 ≥1.5，额外抽 2 张牌</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>抽 3 张牌</t>
+          <t>额外抽 3 张牌</t>
         </is>
       </c>
       <c r="K42" s="11" t="n"/>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>本场战斗中你每次获得金币时，额外获得 2 金币</t>
+          <t>本场战斗中你每次获得金币时，额外获得 3 金币</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>额外 3 金币</t>
+          <t>额外 5 金币</t>
         </is>
       </c>
       <c r="K44" s="11" t="n"/>
@@ -3384,32 +3384,32 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>3能+15金</t>
+          <t>3能</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>风头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>兑现·大炮</t>
+          <t>产金转甲</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
-          <t>造成 50 伤害 ×倍率</t>
+          <t>本场战斗中你每次获得金币时，获得等量格挡</t>
         </is>
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>62 伤害</t>
+          <t>等量 +5 格挡</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>造成 29 伤害 ×倍率；若击杀则本次不清空倍率</t>
+          <t>造成 20 伤害 ×倍率；若击杀则本次不清空倍率</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>36 伤害</t>
+          <t>24 伤害</t>
         </is>
       </c>
     </row>
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>兑现·自伤</t>
+          <t>兑现·格挡</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>获得 10 格挡 ×倍率；自身失去「倍率 ×3」生命</t>
+          <t>获得 12 格挡 ×倍率</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>13 格挡</t>
+          <t>15 格挡</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>对随机敌人造成 9×X 伤害，共 X 次</t>
+          <t>对随机敌人造成 12×X 伤害，共 X 次</t>
         </is>
       </c>
       <c r="J72" s="10" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>对随机敌人造成「弃牌堆张数」伤害（至多 20）</t>
+          <t>对随机敌人造成「弃牌堆张数」伤害（至多 30）</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>至多 28</t>
+          <t>至多 40</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>2能+10金</t>
+          <t>2能</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>特异·金币转格挡</t>
+          <t>花费追踪·转敏捷</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>消耗你一半金币，获得等量格挡（至多 30）</t>
+          <t>本场战斗中你每花费 1 金币，获得 1 点敏捷</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>至多 40</t>
+          <t>每金 +1 力量 +1 敏捷</t>
         </is>
       </c>
     </row>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>1能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>真赌·押手牌</t>
+          <t>真赌·退注</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>造成 8 伤害。赌博：正面 → 15 伤害；反面 → 弃掉 2 张手牌</t>
+          <t>获得 2 点能量。赌博：正面 → 返还本次花费的 5 金币</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>12 / 19</t>
+          <t>3 点能量</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>2能+8金</t>
+          <t>1能+6金</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -4614,17 +4614,17 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>击杀产金·处决</t>
+          <t>特异·格挡返金</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
         <is>
-          <t>对生命值最低的敌人造成 20 伤害；若击杀，获得 15 金币</t>
+          <t>获得 16 格挡，并获得等量金币</t>
         </is>
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>26 伤害</t>
+          <t>20 格挡 / 20 金</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>2能</t>
+          <t>1能+5金</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>费用变为 1</t>
+          <t>费用变为 0</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>2能+18金</t>
+          <t>1能+9金</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>造成 30 伤害；若本场战斗中你掷出过正面，改为 50 伤害</t>
+          <t>造成 36 伤害；若本场战斗中你掷出过正面，改为 60 伤害</t>
         </is>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>38 / 62</t>
+          <t>44 / 72</t>
         </is>
       </c>
     </row>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -1415,7 +1415,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>看场</t>
+          <t>打手</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>盲注</t>
+          <t>跟注</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>兑筹</t>
+          <t>重注</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>假筹</t>
+          <t>假币</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>台规</t>
+          <t>保护费</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>抽佣</t>
+          <t>暗算</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>割禾青</t>
+          <t>见好就收</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>晒冷</t>
+          <t>存钱</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>追数</t>
+          <t>追击</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>割肉</t>
+          <t>止损</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>散码</t>
+          <t>捡漏</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>买码</t>
+          <t>人头费</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>吃水</t>
+          <t>抽税</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>点码</t>
+          <t>记账</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>洗牌</t>
+          <t>典当</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>护池</t>
+          <t>封盘</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>换码</t>
+          <t>充能</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>抽水</t>
+          <t>做手脚</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>反水</t>
+          <t>还手</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>叠码</t>
+          <t>加码</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>保底</t>
+          <t>回收</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>加码</t>
+          <t>底气</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>清码</t>
+          <t>清仓</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>抵押</t>
+          <t>留一手</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>押牌</t>
+          <t>押注</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>截胡</t>
+          <t>过路费</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>换筹</t>
+          <t>提现</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>封口</t>
+          <t>发牌</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5300,6 +5300,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>

--- a/docs/design/gambler-cards.xlsx
+++ b/docs/design/gambler-cards.xlsx
@@ -4992,53 +4992,181 @@
       <c r="B86" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="C86" s="14" t="n"/>
-      <c r="D86" s="14" t="n"/>
-      <c r="E86" s="14" t="n"/>
-      <c r="F86" s="14" t="n"/>
-      <c r="G86" s="14" t="n"/>
-      <c r="H86" s="14" t="n"/>
-      <c r="I86" s="14" t="n"/>
-      <c r="J86" s="15" t="n"/>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>拼命</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>1能</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>赌命·伤害加成</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>你造成的伤害 +「已失去生命」的 10%</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="C87" s="14" t="n"/>
-      <c r="D87" s="14" t="n"/>
-      <c r="E87" s="14" t="n"/>
-      <c r="F87" s="14" t="n"/>
-      <c r="G87" s="14" t="n"/>
-      <c r="H87" s="14" t="n"/>
-      <c r="I87" s="14" t="n"/>
-      <c r="J87" s="15" t="n"/>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>千王</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>2能</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>出千·正面转必正</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>每回合前 1 次掷出正面时，获得 1 次必正</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>前 2 次</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="9" t="n">
         <v>88</v>
       </c>
-      <c r="C88" s="14" t="n"/>
-      <c r="D88" s="14" t="n"/>
-      <c r="E88" s="14" t="n"/>
-      <c r="F88" s="14" t="n"/>
-      <c r="G88" s="14" t="n"/>
-      <c r="H88" s="14" t="n"/>
-      <c r="I88" s="14" t="n"/>
-      <c r="J88" s="15" t="n"/>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>瞒天过海</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>1能+6金</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>出千·本回合全正</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>本回合你接下来的 3 次赌博必为正面</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>4 次</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="C89" s="14" t="n"/>
-      <c r="D89" s="14" t="n"/>
-      <c r="E89" s="14" t="n"/>
-      <c r="F89" s="14" t="n"/>
-      <c r="G89" s="14" t="n"/>
-      <c r="H89" s="14" t="n"/>
-      <c r="I89" s="14" t="n"/>
-      <c r="J89" s="15" t="n"/>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>赌命</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>2能+10金</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>赌命·血线大炮</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>造成「已失去生命」50% 的伤害</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
     </row>
     <row r="90"/>
     <row r="91">
@@ -5084,14 +5212,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B87:J87"/>
+  <mergeCells count="3">
+    <mergeCell ref="B91:J91"/>
     <mergeCell ref="B90:J90"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="B88:J88"/>
     <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B91:J91"/>
-    <mergeCell ref="B86:J86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5103,7 +5227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5300,7 +5424,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
